--- a/packages/preview/jiangcai-jufe-master-thesis/0.1.1/template/tables/字体配置对照表.xlsx
+++ b/packages/preview/jiangcai-jufe-master-thesis/0.1.1/template/tables/字体配置对照表.xlsx
@@ -1,123 +1,129 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
-  <si>
-    <t xml:space="preserve">用途</t>
-  </si>
-  <si>
-    <t xml:space="preserve">字体（族名）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">字体文件</t>
-  </si>
-  <si>
-    <t xml:space="preserve">来源</t>
-  </si>
-  <si>
-    <t xml:space="preserve">正文、脚注、页眉、四五级标题</t>
-  </si>
-  <si>
-    <t xml:space="preserve">宋体（SimSun）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">simsun.ttc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">规范指定</t>
-  </si>
-  <si>
-    <t xml:space="preserve">一至三级标题、封面与声明标题</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黑体（SimHei）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">simhei.ttf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">封面题名、作者与学位等填写项</t>
-  </si>
-  <si>
-    <t xml:space="preserve">楷体（KaiTi）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">simkai.ttf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">中文摘要关键词</t>
-  </si>
-  <si>
-    <t xml:space="preserve">仿宋（FangSong）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">simfang.ttf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">封面“硕士学位论文”字样</t>
-  </si>
-  <si>
-    <t xml:space="preserve">微软雅黑（Microsoft YaHei）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">msyh.ttc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">封面英文标题、中文副标题</t>
-  </si>
-  <si>
-    <t xml:space="preserve">华文中宋（STZhongsong）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STZHONGS.TTF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">西文正文与数字、页码、公式编号</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Times New Roman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">times.ttf 等 4 个字重</t>
-  </si>
-  <si>
-    <t xml:space="preserve">数学公式</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New Computer Modern Math</t>
-  </si>
-  <si>
-    <t xml:space="preserve">—（编译器内置）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">编译器内置</t>
-  </si>
-  <si>
-    <t xml:space="preserve">代码块与行内代码</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Courier New</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cour.ttf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">模板自选</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
+  <si>
+    <t>用途</t>
+  </si>
+  <si>
+    <t>字体（族名）</t>
+  </si>
+  <si>
+    <t>字体文件</t>
+  </si>
+  <si>
+    <t>来源</t>
+  </si>
+  <si>
+    <t>正文、脚注、页眉等</t>
+  </si>
+  <si>
+    <t>宋体（SimSun）</t>
+  </si>
+  <si>
+    <t>simsun.ttc</t>
+  </si>
+  <si>
+    <t>规范指定</t>
+  </si>
+  <si>
+    <t>一至三级标题、封面等</t>
+  </si>
+  <si>
+    <t>黑体（SimHei）</t>
+  </si>
+  <si>
+    <t>simhei.ttf</t>
+  </si>
+  <si>
+    <t>封面题名、作者等填写项</t>
+  </si>
+  <si>
+    <t>楷体（KaiTi）</t>
+  </si>
+  <si>
+    <t>simkai.ttf</t>
+  </si>
+  <si>
+    <t>中文摘要关键词</t>
+  </si>
+  <si>
+    <t>仿宋（FangSong）</t>
+  </si>
+  <si>
+    <t>simfang.ttf</t>
+  </si>
+  <si>
+    <t>封面“硕士学位论文”</t>
+  </si>
+  <si>
+    <t>微软雅黑（Microsoft YaHei）</t>
+  </si>
+  <si>
+    <t>msyh.ttc</t>
+  </si>
+  <si>
+    <t>封面英文标题与副标题</t>
+  </si>
+  <si>
+    <t>华文中宋（STZhongsong）</t>
+  </si>
+  <si>
+    <t>STZHONGS.TTF</t>
+  </si>
+  <si>
+    <t>西文、数字、页码与公式编号</t>
+  </si>
+  <si>
+    <t>Times New Roman</t>
+  </si>
+  <si>
+    <t>times.ttf 等 4 个字重</t>
+  </si>
+  <si>
+    <t>数学公式</t>
+  </si>
+  <si>
+    <t>New Computer Modern Math</t>
+  </si>
+  <si>
+    <t>—（编译器内置）</t>
+  </si>
+  <si>
+    <t>编译器内置</t>
+  </si>
+  <si>
+    <t>代码块与行内代码</t>
+  </si>
+  <si>
+    <t>Courier New</t>
+  </si>
+  <si>
+    <t>cour.ttf</t>
+  </si>
+  <si>
+    <t>模板自选</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -145,11 +151,24 @@
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -159,46 +178,106 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -206,31 +285,217 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
-        <a:effectStyle/>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -244,7 +509,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -258,7 +523,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -272,7 +537,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -286,7 +551,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -300,7 +565,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -314,7 +579,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -328,7 +593,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -342,7 +607,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -356,7 +621,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -371,5 +636,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>